--- a/BaoCao_Final/9.1.TestCaseSprint1.xlsx
+++ b/BaoCao_Final/9.1.TestCaseSprint1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="e:\Downloads\Document\BaoCao_Final(1)\BaoCao_Final\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xtung\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3474161-6140-4E83-A42E-FC0C7EDCFC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78825E3B-4E54-4714-BF66-7D74EFDAC939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trường hợp kiểm thử" sheetId="1" r:id="rId1"/>
@@ -2645,16 +2645,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2681,10 +2681,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4084,25 +4084,25 @@
       <c r="A1" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:13" ht="33.6">
       <c r="A3" s="8"/>
@@ -4168,64 +4168,64 @@
     </row>
     <row r="6" spans="1:13" ht="409.05" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47" t="s">
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47" t="s">
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="47"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47" t="s">
+      <c r="A8" s="48"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47" t="s">
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="47"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="47"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
+      <c r="A9" s="48"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -4244,24 +4244,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="47"/>
+      <c r="M9" s="48"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="49" t="s">
         <v>520</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
     </row>
     <row r="11" spans="1:13" ht="67.2">
       <c r="A11" s="14" t="s">
@@ -4286,7 +4286,7 @@
         <v>63</v>
       </c>
       <c r="H11" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>112</v>
@@ -4295,7 +4295,7 @@
         <v>63</v>
       </c>
       <c r="K11" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>112</v>
@@ -4325,7 +4325,7 @@
         <v>63</v>
       </c>
       <c r="H12" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>112</v>
@@ -4334,7 +4334,7 @@
         <v>63</v>
       </c>
       <c r="K12" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>112</v>
@@ -4364,7 +4364,7 @@
         <v>63</v>
       </c>
       <c r="H13" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>112</v>
@@ -4373,7 +4373,7 @@
         <v>63</v>
       </c>
       <c r="K13" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>112</v>
@@ -4381,21 +4381,21 @@
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="49" t="s">
         <v>486</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="49"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="49"/>
     </row>
     <row r="15" spans="1:13" ht="50.4">
       <c r="A15" s="14" t="s">
@@ -4420,7 +4420,7 @@
         <v>63</v>
       </c>
       <c r="H15" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>112</v>
@@ -4429,7 +4429,7 @@
         <v>63</v>
       </c>
       <c r="K15" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>112</v>
@@ -4457,7 +4457,7 @@
         <v>63</v>
       </c>
       <c r="H16" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>112</v>
@@ -4466,7 +4466,7 @@
         <v>63</v>
       </c>
       <c r="K16" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>112</v>
@@ -4494,7 +4494,7 @@
         <v>63</v>
       </c>
       <c r="H17" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>112</v>
@@ -4503,7 +4503,7 @@
         <v>63</v>
       </c>
       <c r="K17" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>112</v>
@@ -4531,7 +4531,7 @@
         <v>63</v>
       </c>
       <c r="H18" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>112</v>
@@ -4540,7 +4540,7 @@
         <v>63</v>
       </c>
       <c r="K18" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>112</v>
@@ -4568,7 +4568,7 @@
         <v>63</v>
       </c>
       <c r="H19" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>112</v>
@@ -4577,7 +4577,7 @@
         <v>63</v>
       </c>
       <c r="K19" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>112</v>
@@ -4605,7 +4605,7 @@
         <v>63</v>
       </c>
       <c r="H20" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>112</v>
@@ -4614,7 +4614,7 @@
         <v>63</v>
       </c>
       <c r="K20" s="12">
-        <v>46282</v>
+        <v>46260</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>112</v>
@@ -4623,6 +4623,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="A10:M10"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A7:A9"/>
@@ -4631,13 +4638,6 @@
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="E7:E9"/>
     <mergeCell ref="F7:F9"/>
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="A10:M10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="J15:J20 J11:J13" xr:uid="{2C85C8A1-E250-4D17-A040-3B9A0E8D82A3}">
@@ -4675,25 +4675,25 @@
       <c r="A1" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="47" t="s">
         <v>568</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:13" ht="33.6">
       <c r="A3" s="8"/>
@@ -4759,64 +4759,64 @@
     </row>
     <row r="6" spans="1:13" ht="409.05" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47" t="s">
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47" t="s">
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="47"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47" t="s">
+      <c r="A8" s="48"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47" t="s">
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="47"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="47"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
+      <c r="A9" s="48"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -4835,24 +4835,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="47"/>
+      <c r="M9" s="48"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="49" t="s">
         <v>615</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
     </row>
     <row r="11" spans="1:13" ht="33.6">
       <c r="A11" s="14" t="s">
@@ -4877,7 +4877,7 @@
         <v>63</v>
       </c>
       <c r="H11" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>112</v>
@@ -4886,7 +4886,7 @@
         <v>63</v>
       </c>
       <c r="K11" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>112</v>
@@ -4914,7 +4914,7 @@
         <v>63</v>
       </c>
       <c r="H12" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>112</v>
@@ -4923,7 +4923,7 @@
         <v>63</v>
       </c>
       <c r="K12" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>112</v>
@@ -4953,7 +4953,7 @@
         <v>63</v>
       </c>
       <c r="H13" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>112</v>
@@ -4962,7 +4962,7 @@
         <v>63</v>
       </c>
       <c r="K13" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>112</v>
@@ -4990,7 +4990,7 @@
         <v>63</v>
       </c>
       <c r="H14" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>112</v>
@@ -4999,7 +4999,7 @@
         <v>63</v>
       </c>
       <c r="K14" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>112</v>
@@ -5007,21 +5007,21 @@
       <c r="M14" s="8"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="49" t="s">
         <v>616</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
     </row>
     <row r="16" spans="1:13" ht="33.6">
       <c r="A16" s="14" t="s">
@@ -5046,7 +5046,7 @@
         <v>63</v>
       </c>
       <c r="H16" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>112</v>
@@ -5055,7 +5055,7 @@
         <v>63</v>
       </c>
       <c r="K16" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>112</v>
@@ -5083,7 +5083,7 @@
         <v>63</v>
       </c>
       <c r="H17" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>112</v>
@@ -5092,7 +5092,7 @@
         <v>63</v>
       </c>
       <c r="K17" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>112</v>
@@ -5120,7 +5120,7 @@
         <v>63</v>
       </c>
       <c r="H18" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>112</v>
@@ -5129,7 +5129,7 @@
         <v>63</v>
       </c>
       <c r="K18" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>112</v>
@@ -5157,7 +5157,7 @@
         <v>63</v>
       </c>
       <c r="H19" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>112</v>
@@ -5166,7 +5166,7 @@
         <v>63</v>
       </c>
       <c r="K19" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>112</v>
@@ -5196,7 +5196,7 @@
         <v>63</v>
       </c>
       <c r="H20" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>112</v>
@@ -5205,7 +5205,7 @@
         <v>63</v>
       </c>
       <c r="K20" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>112</v>
@@ -5233,7 +5233,7 @@
         <v>63</v>
       </c>
       <c r="H21" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>112</v>
@@ -5242,7 +5242,7 @@
         <v>63</v>
       </c>
       <c r="K21" s="12">
-        <v>46282</v>
+        <v>46262</v>
       </c>
       <c r="L21" s="13" t="s">
         <v>112</v>
@@ -5251,6 +5251,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="A10:M10"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A7:A9"/>
@@ -5259,13 +5266,6 @@
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="E7:E9"/>
     <mergeCell ref="F7:F9"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="A10:M10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="J16:J21 J11:J14" xr:uid="{28045B58-661C-4692-8654-971E512A91B0}">
@@ -5303,25 +5303,25 @@
       <c r="A1" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:13" ht="33.6">
       <c r="A3" s="8"/>
@@ -5387,64 +5387,64 @@
     </row>
     <row r="6" spans="1:13" ht="409.05" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47" t="s">
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47" t="s">
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="47"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47" t="s">
+      <c r="A8" s="48"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47" t="s">
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="47"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="47"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
+      <c r="A9" s="48"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -5463,24 +5463,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="47"/>
+      <c r="M9" s="48"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="49" t="s">
         <v>617</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
     </row>
     <row r="11" spans="1:13" ht="50.4">
       <c r="A11" s="14" t="s">
@@ -5505,7 +5505,7 @@
         <v>63</v>
       </c>
       <c r="H11" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>112</v>
@@ -5514,7 +5514,7 @@
         <v>63</v>
       </c>
       <c r="K11" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>112</v>
@@ -5542,7 +5542,7 @@
         <v>63</v>
       </c>
       <c r="H12" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>112</v>
@@ -5551,7 +5551,7 @@
         <v>63</v>
       </c>
       <c r="K12" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>112</v>
@@ -5581,7 +5581,7 @@
         <v>63</v>
       </c>
       <c r="H13" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>112</v>
@@ -5590,7 +5590,7 @@
         <v>63</v>
       </c>
       <c r="K13" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>112</v>
@@ -5598,21 +5598,21 @@
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="49" t="s">
         <v>632</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="49"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="49"/>
     </row>
     <row r="15" spans="1:13" ht="50.4">
       <c r="A15" s="14" t="s">
@@ -5635,7 +5635,7 @@
         <v>63</v>
       </c>
       <c r="H15" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>112</v>
@@ -5644,7 +5644,7 @@
         <v>63</v>
       </c>
       <c r="K15" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>112</v>
@@ -5672,7 +5672,7 @@
         <v>63</v>
       </c>
       <c r="H16" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>112</v>
@@ -5681,7 +5681,7 @@
         <v>63</v>
       </c>
       <c r="K16" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>112</v>
@@ -5709,7 +5709,7 @@
         <v>63</v>
       </c>
       <c r="H17" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>112</v>
@@ -5718,7 +5718,7 @@
         <v>63</v>
       </c>
       <c r="K17" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>112</v>
@@ -5746,7 +5746,7 @@
         <v>63</v>
       </c>
       <c r="H18" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>112</v>
@@ -5755,7 +5755,7 @@
         <v>63</v>
       </c>
       <c r="K18" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>112</v>
@@ -5783,7 +5783,7 @@
         <v>63</v>
       </c>
       <c r="H19" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>112</v>
@@ -5792,7 +5792,7 @@
         <v>63</v>
       </c>
       <c r="K19" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>112</v>
@@ -5822,7 +5822,7 @@
         <v>63</v>
       </c>
       <c r="H20" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>112</v>
@@ -5831,7 +5831,7 @@
         <v>63</v>
       </c>
       <c r="K20" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>112</v>
@@ -5859,7 +5859,7 @@
         <v>63</v>
       </c>
       <c r="H21" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>112</v>
@@ -5868,7 +5868,7 @@
         <v>63</v>
       </c>
       <c r="K21" s="12">
-        <v>46282</v>
+        <v>46263</v>
       </c>
       <c r="L21" s="13" t="s">
         <v>112</v>
@@ -5877,6 +5877,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="A10:M10"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A7:A9"/>
@@ -5885,13 +5892,6 @@
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="E7:E9"/>
     <mergeCell ref="F7:F9"/>
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="A10:M10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="J11:J13 J15:J21" xr:uid="{6127085D-3544-4E6A-B486-FA5180FA76F7}">
@@ -5929,25 +5929,25 @@
       <c r="A1" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:13" ht="33.6">
       <c r="A3" s="8"/>
@@ -6013,64 +6013,64 @@
     </row>
     <row r="6" spans="1:13" ht="409.05" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47" t="s">
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47" t="s">
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="47"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47" t="s">
+      <c r="A8" s="48"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47" t="s">
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="47"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="47"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
+      <c r="A9" s="48"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -6089,24 +6089,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="47"/>
+      <c r="M9" s="48"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="49" t="s">
         <v>666</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
     </row>
     <row r="11" spans="1:13" ht="33.6">
       <c r="A11" s="14" t="s">
@@ -6131,7 +6131,7 @@
         <v>63</v>
       </c>
       <c r="H11" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>112</v>
@@ -6140,7 +6140,7 @@
         <v>63</v>
       </c>
       <c r="K11" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>112</v>
@@ -6168,7 +6168,7 @@
         <v>63</v>
       </c>
       <c r="H12" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>112</v>
@@ -6177,7 +6177,7 @@
         <v>63</v>
       </c>
       <c r="K12" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>112</v>
@@ -6205,7 +6205,7 @@
         <v>63</v>
       </c>
       <c r="H13" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>112</v>
@@ -6214,7 +6214,7 @@
         <v>63</v>
       </c>
       <c r="K13" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>112</v>
@@ -6244,7 +6244,7 @@
         <v>63</v>
       </c>
       <c r="H14" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>112</v>
@@ -6253,7 +6253,7 @@
         <v>63</v>
       </c>
       <c r="K14" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>112</v>
@@ -6261,21 +6261,21 @@
       <c r="M14" s="8"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="49" t="s">
         <v>632</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
     </row>
     <row r="16" spans="1:13" ht="50.4">
       <c r="A16" s="14" t="s">
@@ -6298,7 +6298,7 @@
         <v>63</v>
       </c>
       <c r="H16" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>112</v>
@@ -6307,7 +6307,7 @@
         <v>63</v>
       </c>
       <c r="K16" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>112</v>
@@ -6335,7 +6335,7 @@
         <v>63</v>
       </c>
       <c r="H17" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>112</v>
@@ -6344,7 +6344,7 @@
         <v>63</v>
       </c>
       <c r="K17" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>112</v>
@@ -6372,7 +6372,7 @@
         <v>707</v>
       </c>
       <c r="H18" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>112</v>
@@ -6381,7 +6381,7 @@
         <v>707</v>
       </c>
       <c r="K18" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>112</v>
@@ -6411,7 +6411,7 @@
         <v>63</v>
       </c>
       <c r="H19" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>112</v>
@@ -6420,7 +6420,7 @@
         <v>63</v>
       </c>
       <c r="K19" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>112</v>
@@ -6450,7 +6450,7 @@
         <v>63</v>
       </c>
       <c r="H20" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>112</v>
@@ -6459,7 +6459,7 @@
         <v>63</v>
       </c>
       <c r="K20" s="12">
-        <v>46282</v>
+        <v>46264</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>112</v>
@@ -6468,6 +6468,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="A10:M10"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A7:A9"/>
@@ -6476,13 +6483,6 @@
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="E7:E9"/>
     <mergeCell ref="F7:F9"/>
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="A10:M10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="J16:J20 J11:J14" xr:uid="{3288FB60-9A0A-4DD8-8411-2F3ACA8502B6}">
@@ -6515,25 +6515,25 @@
       <c r="A1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:13" ht="16.8">
       <c r="A2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:13" ht="33.6">
       <c r="A3" s="23"/>
@@ -6599,64 +6599,64 @@
     </row>
     <row r="6" spans="1:13" ht="361.5" customHeight="1"/>
     <row r="7" spans="1:13" ht="16.8">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="59" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="58" t="s">
+      <c r="D7" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="58" t="s">
+      <c r="E7" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="58" t="s">
+      <c r="F7" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="58" t="s">
+      <c r="G7" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58" t="s">
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58" t="s">
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.8">
-      <c r="A8" s="58"/>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58" t="s">
+      <c r="A8" s="59"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58" t="s">
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="58"/>
-      <c r="L8" s="58"/>
-      <c r="M8" s="58"/>
+      <c r="K8" s="59"/>
+      <c r="L8" s="59"/>
+      <c r="M8" s="59"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="58"/>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
+      <c r="A9" s="59"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
       <c r="G9" s="16" t="s">
         <v>59</v>
       </c>
@@ -6675,24 +6675,24 @@
       <c r="L9" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="58"/>
+      <c r="M9" s="59"/>
     </row>
     <row r="10" spans="1:13" ht="16.8">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="49" t="s">
         <v>139</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
     </row>
     <row r="11" spans="1:13" ht="50.4">
       <c r="A11" s="11" t="s">
@@ -6717,7 +6717,7 @@
         <v>63</v>
       </c>
       <c r="H11" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>112</v>
@@ -6726,7 +6726,7 @@
         <v>63</v>
       </c>
       <c r="K11" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>112</v>
@@ -6754,7 +6754,7 @@
         <v>63</v>
       </c>
       <c r="H12" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>112</v>
@@ -6763,7 +6763,7 @@
         <v>63</v>
       </c>
       <c r="K12" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>112</v>
@@ -6791,7 +6791,7 @@
         <v>63</v>
       </c>
       <c r="H13" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>112</v>
@@ -6800,7 +6800,7 @@
         <v>63</v>
       </c>
       <c r="K13" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>112</v>
@@ -6828,7 +6828,7 @@
         <v>707</v>
       </c>
       <c r="H14" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>112</v>
@@ -6837,7 +6837,7 @@
         <v>707</v>
       </c>
       <c r="K14" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>112</v>
@@ -6865,7 +6865,7 @@
         <v>63</v>
       </c>
       <c r="H15" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>112</v>
@@ -6874,7 +6874,7 @@
         <v>63</v>
       </c>
       <c r="K15" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>112</v>
@@ -6902,7 +6902,7 @@
         <v>63</v>
       </c>
       <c r="H16" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>112</v>
@@ -6911,7 +6911,7 @@
         <v>63</v>
       </c>
       <c r="K16" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>112</v>
@@ -6919,21 +6919,21 @@
       <c r="M16" s="14"/>
     </row>
     <row r="17" spans="1:13" ht="16.8">
-      <c r="A17" s="59" t="s">
+      <c r="A17" s="58" t="s">
         <v>138</v>
       </c>
-      <c r="B17" s="59"/>
-      <c r="C17" s="59"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="59"/>
-      <c r="I17" s="59"/>
-      <c r="J17" s="59"/>
-      <c r="K17" s="59"/>
-      <c r="L17" s="59"/>
-      <c r="M17" s="59"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="58"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="58"/>
     </row>
     <row r="18" spans="1:13" ht="50.4">
       <c r="A18" s="15" t="s">
@@ -6958,7 +6958,7 @@
         <v>63</v>
       </c>
       <c r="H18" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>112</v>
@@ -6967,7 +6967,7 @@
         <v>63</v>
       </c>
       <c r="K18" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>112</v>
@@ -6997,7 +6997,7 @@
         <v>63</v>
       </c>
       <c r="H19" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>112</v>
@@ -7006,7 +7006,7 @@
         <v>63</v>
       </c>
       <c r="K19" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>112</v>
@@ -7034,7 +7034,7 @@
         <v>63</v>
       </c>
       <c r="H20" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>112</v>
@@ -7043,7 +7043,7 @@
         <v>63</v>
       </c>
       <c r="K20" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>112</v>
@@ -7071,7 +7071,7 @@
         <v>63</v>
       </c>
       <c r="H21" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>112</v>
@@ -7080,7 +7080,7 @@
         <v>63</v>
       </c>
       <c r="K21" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="L21" s="13" t="s">
         <v>112</v>
@@ -7108,7 +7108,7 @@
         <v>63</v>
       </c>
       <c r="H22" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>112</v>
@@ -7117,7 +7117,7 @@
         <v>63</v>
       </c>
       <c r="K22" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>112</v>
@@ -7145,7 +7145,7 @@
         <v>63</v>
       </c>
       <c r="H23" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>112</v>
@@ -7154,7 +7154,7 @@
         <v>63</v>
       </c>
       <c r="K23" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="L23" s="13" t="s">
         <v>112</v>
@@ -7184,7 +7184,7 @@
         <v>63</v>
       </c>
       <c r="H24" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="I24" s="13" t="s">
         <v>112</v>
@@ -7193,7 +7193,7 @@
         <v>63</v>
       </c>
       <c r="K24" s="12">
-        <v>46282</v>
+        <v>46252</v>
       </c>
       <c r="L24" s="13" t="s">
         <v>112</v>
@@ -7571,13 +7571,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A17:M17"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="A10:M10"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A7:A9"/>
@@ -7586,6 +7579,13 @@
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="E7:E9"/>
     <mergeCell ref="F7:F9"/>
+    <mergeCell ref="A17:M17"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="A10:M10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="J11:J16 G18:G23 J18:J24" xr:uid="{E0A3F6D6-9AE8-4147-9E0D-21A4039E463B}">
@@ -7624,25 +7624,25 @@
       <c r="A1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="23"/>
@@ -7708,64 +7708,64 @@
     </row>
     <row r="6" spans="1:13" ht="287.55" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="59" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="58" t="s">
+      <c r="D7" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="58" t="s">
+      <c r="E7" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="58" t="s">
+      <c r="F7" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="58" t="s">
+      <c r="G7" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58" t="s">
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58" t="s">
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="58"/>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58" t="s">
+      <c r="A8" s="59"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58" t="s">
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="58"/>
-      <c r="L8" s="58"/>
-      <c r="M8" s="58"/>
+      <c r="K8" s="59"/>
+      <c r="L8" s="59"/>
+      <c r="M8" s="59"/>
     </row>
     <row r="9" spans="1:13" ht="49.5" customHeight="1">
-      <c r="A9" s="58"/>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
+      <c r="A9" s="59"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
       <c r="G9" s="16" t="s">
         <v>59</v>
       </c>
@@ -7784,24 +7784,24 @@
       <c r="L9" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="58"/>
+      <c r="M9" s="59"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="49" t="s">
         <v>137</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
     </row>
     <row r="11" spans="1:13" ht="50.4">
       <c r="A11" s="11" t="s">
@@ -7826,7 +7826,7 @@
         <v>63</v>
       </c>
       <c r="H11" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>112</v>
@@ -7835,7 +7835,7 @@
         <v>63</v>
       </c>
       <c r="K11" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>112</v>
@@ -7863,7 +7863,7 @@
         <v>63</v>
       </c>
       <c r="H12" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>112</v>
@@ -7872,7 +7872,7 @@
         <v>63</v>
       </c>
       <c r="K12" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>112</v>
@@ -7900,7 +7900,7 @@
         <v>63</v>
       </c>
       <c r="H13" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>112</v>
@@ -7909,7 +7909,7 @@
         <v>63</v>
       </c>
       <c r="K13" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>112</v>
@@ -7937,7 +7937,7 @@
         <v>63</v>
       </c>
       <c r="H14" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>112</v>
@@ -7946,7 +7946,7 @@
         <v>63</v>
       </c>
       <c r="K14" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>112</v>
@@ -7954,21 +7954,21 @@
       <c r="M14" s="8"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="49" t="s">
         <v>136</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
     </row>
     <row r="16" spans="1:13" ht="50.4">
       <c r="A16" s="14" t="s">
@@ -7991,7 +7991,7 @@
         <v>63</v>
       </c>
       <c r="H16" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>112</v>
@@ -8000,7 +8000,7 @@
         <v>63</v>
       </c>
       <c r="K16" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>112</v>
@@ -8028,7 +8028,7 @@
         <v>63</v>
       </c>
       <c r="H17" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>112</v>
@@ -8037,7 +8037,7 @@
         <v>63</v>
       </c>
       <c r="K17" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>112</v>
@@ -8065,7 +8065,7 @@
         <v>63</v>
       </c>
       <c r="H18" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>112</v>
@@ -8074,7 +8074,7 @@
         <v>63</v>
       </c>
       <c r="K18" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>112</v>
@@ -8102,7 +8102,7 @@
         <v>63</v>
       </c>
       <c r="H19" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>112</v>
@@ -8111,7 +8111,7 @@
         <v>63</v>
       </c>
       <c r="K19" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>112</v>
@@ -8139,7 +8139,7 @@
         <v>63</v>
       </c>
       <c r="H20" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>112</v>
@@ -8148,7 +8148,7 @@
         <v>63</v>
       </c>
       <c r="K20" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>112</v>
@@ -8176,7 +8176,7 @@
         <v>63</v>
       </c>
       <c r="H21" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>112</v>
@@ -8185,7 +8185,7 @@
         <v>63</v>
       </c>
       <c r="K21" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="L21" s="13" t="s">
         <v>112</v>
@@ -8213,7 +8213,7 @@
         <v>63</v>
       </c>
       <c r="H22" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>112</v>
@@ -8222,7 +8222,7 @@
         <v>63</v>
       </c>
       <c r="K22" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>112</v>
@@ -8250,7 +8250,7 @@
         <v>63</v>
       </c>
       <c r="H23" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>112</v>
@@ -8259,7 +8259,7 @@
         <v>63</v>
       </c>
       <c r="K23" s="12">
-        <v>46282</v>
+        <v>46253</v>
       </c>
       <c r="L23" s="13" t="s">
         <v>112</v>
@@ -8664,13 +8664,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A15:M15"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="A10:M10"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A7:A9"/>
@@ -8679,6 +8672,13 @@
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="E7:E9"/>
     <mergeCell ref="F7:F9"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="A10:M10"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <dataValidations count="1">
@@ -8717,25 +8717,25 @@
       <c r="A1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:13" ht="16.8">
       <c r="A2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:13" ht="33.6">
       <c r="A3" s="23"/>
@@ -8801,64 +8801,64 @@
     </row>
     <row r="6" spans="1:13" ht="277.05" customHeight="1"/>
     <row r="7" spans="1:13" ht="16.8">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="59" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="58" t="s">
+      <c r="D7" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="58" t="s">
+      <c r="E7" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="58" t="s">
+      <c r="F7" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="58" t="s">
+      <c r="G7" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58" t="s">
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+      <c r="J7" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58" t="s">
+      <c r="K7" s="59"/>
+      <c r="L7" s="59"/>
+      <c r="M7" s="59" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.8">
-      <c r="A8" s="58"/>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58" t="s">
+      <c r="A8" s="59"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58" t="s">
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+      <c r="J8" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="58"/>
-      <c r="L8" s="58"/>
-      <c r="M8" s="58"/>
+      <c r="K8" s="59"/>
+      <c r="L8" s="59"/>
+      <c r="M8" s="59"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="58"/>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
+      <c r="A9" s="59"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
       <c r="G9" s="16" t="s">
         <v>59</v>
       </c>
@@ -8877,24 +8877,24 @@
       <c r="L9" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="58"/>
+      <c r="M9" s="59"/>
     </row>
     <row r="10" spans="1:13" ht="16.8">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="49" t="s">
         <v>247</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
     </row>
     <row r="11" spans="1:13" ht="33.6">
       <c r="A11" s="11" t="s">
@@ -8919,7 +8919,7 @@
         <v>63</v>
       </c>
       <c r="H11" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>112</v>
@@ -8928,7 +8928,7 @@
         <v>63</v>
       </c>
       <c r="K11" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>112</v>
@@ -8956,7 +8956,7 @@
         <v>63</v>
       </c>
       <c r="H12" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>112</v>
@@ -8965,7 +8965,7 @@
         <v>63</v>
       </c>
       <c r="K12" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>112</v>
@@ -8995,7 +8995,7 @@
         <v>63</v>
       </c>
       <c r="H13" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>112</v>
@@ -9004,7 +9004,7 @@
         <v>63</v>
       </c>
       <c r="K13" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>112</v>
@@ -9034,7 +9034,7 @@
         <v>63</v>
       </c>
       <c r="H14" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>112</v>
@@ -9043,7 +9043,7 @@
         <v>63</v>
       </c>
       <c r="K14" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>112</v>
@@ -9071,7 +9071,7 @@
         <v>63</v>
       </c>
       <c r="H15" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>112</v>
@@ -9080,7 +9080,7 @@
         <v>63</v>
       </c>
       <c r="K15" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>112</v>
@@ -9088,21 +9088,21 @@
       <c r="M15" s="8"/>
     </row>
     <row r="16" spans="1:13" ht="16.8">
-      <c r="A16" s="46" t="s">
+      <c r="A16" s="49" t="s">
         <v>246</v>
       </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="46"/>
-      <c r="D16" s="46"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="46"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="46"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="49"/>
+      <c r="L16" s="49"/>
+      <c r="M16" s="49"/>
     </row>
     <row r="17" spans="1:13" ht="67.2">
       <c r="A17" s="14" t="s">
@@ -9125,7 +9125,7 @@
         <v>63</v>
       </c>
       <c r="H17" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>112</v>
@@ -9134,7 +9134,7 @@
         <v>63</v>
       </c>
       <c r="K17" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>112</v>
@@ -9162,7 +9162,7 @@
         <v>63</v>
       </c>
       <c r="H18" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>112</v>
@@ -9171,7 +9171,7 @@
         <v>63</v>
       </c>
       <c r="K18" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>112</v>
@@ -9199,7 +9199,7 @@
         <v>63</v>
       </c>
       <c r="H19" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>112</v>
@@ -9208,7 +9208,7 @@
         <v>63</v>
       </c>
       <c r="K19" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>112</v>
@@ -9236,7 +9236,7 @@
         <v>63</v>
       </c>
       <c r="H20" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>112</v>
@@ -9245,7 +9245,7 @@
         <v>63</v>
       </c>
       <c r="K20" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>112</v>
@@ -9275,7 +9275,7 @@
         <v>63</v>
       </c>
       <c r="H21" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>112</v>
@@ -9284,7 +9284,7 @@
         <v>63</v>
       </c>
       <c r="K21" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L21" s="13" t="s">
         <v>112</v>
@@ -9312,7 +9312,7 @@
         <v>63</v>
       </c>
       <c r="H22" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>112</v>
@@ -9321,7 +9321,7 @@
         <v>63</v>
       </c>
       <c r="K22" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>112</v>
@@ -9349,7 +9349,7 @@
         <v>63</v>
       </c>
       <c r="H23" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>112</v>
@@ -9358,7 +9358,7 @@
         <v>63</v>
       </c>
       <c r="K23" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L23" s="13" t="s">
         <v>112</v>
@@ -9386,7 +9386,7 @@
         <v>63</v>
       </c>
       <c r="H24" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="I24" s="13" t="s">
         <v>112</v>
@@ -9395,7 +9395,7 @@
         <v>63</v>
       </c>
       <c r="K24" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L24" s="13" t="s">
         <v>112</v>
@@ -9423,7 +9423,7 @@
         <v>63</v>
       </c>
       <c r="H25" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>112</v>
@@ -9432,7 +9432,7 @@
         <v>63</v>
       </c>
       <c r="K25" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L25" s="13" t="s">
         <v>112</v>
@@ -9462,7 +9462,7 @@
         <v>63</v>
       </c>
       <c r="H26" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="I26" s="13" t="s">
         <v>112</v>
@@ -9471,7 +9471,7 @@
         <v>63</v>
       </c>
       <c r="K26" s="12">
-        <v>46282</v>
+        <v>46254</v>
       </c>
       <c r="L26" s="13" t="s">
         <v>112</v>
@@ -9480,6 +9480,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="A10:M10"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A7:A9"/>
@@ -9488,13 +9495,6 @@
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="E7:E9"/>
     <mergeCell ref="F7:F9"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="A10:M10"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <dataValidations count="1">
@@ -9533,25 +9533,25 @@
       <c r="A1" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:13" ht="33.6">
       <c r="A3" s="8"/>
@@ -9617,64 +9617,64 @@
     </row>
     <row r="6" spans="1:13" ht="380.55" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47" t="s">
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47" t="s">
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.05" customHeight="1">
-      <c r="A8" s="47"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47" t="s">
+      <c r="A8" s="48"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47" t="s">
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="47"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="47"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
+      <c r="A9" s="48"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -9693,24 +9693,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="47"/>
+      <c r="M9" s="48"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="49" t="s">
         <v>322</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
     </row>
     <row r="11" spans="1:13" ht="33.6">
       <c r="A11" s="14" t="s">
@@ -9735,7 +9735,7 @@
         <v>63</v>
       </c>
       <c r="H11" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>112</v>
@@ -9744,7 +9744,7 @@
         <v>63</v>
       </c>
       <c r="K11" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>112</v>
@@ -9772,7 +9772,7 @@
         <v>63</v>
       </c>
       <c r="H12" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>112</v>
@@ -9781,7 +9781,7 @@
         <v>63</v>
       </c>
       <c r="K12" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>112</v>
@@ -9811,7 +9811,7 @@
         <v>63</v>
       </c>
       <c r="H13" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>112</v>
@@ -9820,7 +9820,7 @@
         <v>63</v>
       </c>
       <c r="K13" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>112</v>
@@ -9828,21 +9828,21 @@
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="49" t="s">
         <v>323</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="49"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="49"/>
     </row>
     <row r="15" spans="1:13" ht="33.6">
       <c r="A15" s="14" t="s">
@@ -9865,7 +9865,7 @@
         <v>63</v>
       </c>
       <c r="H15" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>112</v>
@@ -9874,7 +9874,7 @@
         <v>63</v>
       </c>
       <c r="K15" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>112</v>
@@ -9902,7 +9902,7 @@
         <v>63</v>
       </c>
       <c r="H16" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>112</v>
@@ -9911,7 +9911,7 @@
         <v>63</v>
       </c>
       <c r="K16" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>112</v>
@@ -9939,7 +9939,7 @@
         <v>63</v>
       </c>
       <c r="H17" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>112</v>
@@ -9948,7 +9948,7 @@
         <v>63</v>
       </c>
       <c r="K17" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>112</v>
@@ -9978,7 +9978,7 @@
         <v>63</v>
       </c>
       <c r="H18" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>112</v>
@@ -9987,7 +9987,7 @@
         <v>63</v>
       </c>
       <c r="K18" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>112</v>
@@ -10015,7 +10015,7 @@
         <v>63</v>
       </c>
       <c r="H19" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>112</v>
@@ -10024,7 +10024,7 @@
         <v>63</v>
       </c>
       <c r="K19" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>112</v>
@@ -10032,21 +10032,21 @@
       <c r="M19" s="8"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="49" t="s">
         <v>321</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="46"/>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="46"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
+      <c r="K20" s="49"/>
+      <c r="L20" s="49"/>
+      <c r="M20" s="49"/>
     </row>
     <row r="21" spans="1:13" ht="33.6">
       <c r="A21" s="14" t="s">
@@ -10071,7 +10071,7 @@
         <v>63</v>
       </c>
       <c r="H21" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>112</v>
@@ -10080,7 +10080,7 @@
         <v>63</v>
       </c>
       <c r="K21" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L21" s="13" t="s">
         <v>112</v>
@@ -10108,7 +10108,7 @@
         <v>63</v>
       </c>
       <c r="H22" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>112</v>
@@ -10117,7 +10117,7 @@
         <v>63</v>
       </c>
       <c r="K22" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>112</v>
@@ -10147,7 +10147,7 @@
         <v>63</v>
       </c>
       <c r="H23" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>112</v>
@@ -10156,7 +10156,7 @@
         <v>63</v>
       </c>
       <c r="K23" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L23" s="13" t="s">
         <v>112</v>
@@ -10164,21 +10164,21 @@
       <c r="M23" s="8"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="49" t="s">
         <v>320</v>
       </c>
-      <c r="B24" s="46"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="46"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="49"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="49"/>
+      <c r="I24" s="49"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="49"/>
+      <c r="L24" s="49"/>
+      <c r="M24" s="49"/>
     </row>
     <row r="25" spans="1:13" ht="33.6">
       <c r="A25" s="14" t="s">
@@ -10201,7 +10201,7 @@
         <v>63</v>
       </c>
       <c r="H25" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>112</v>
@@ -10210,7 +10210,7 @@
         <v>63</v>
       </c>
       <c r="K25" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L25" s="13" t="s">
         <v>112</v>
@@ -10238,7 +10238,7 @@
         <v>63</v>
       </c>
       <c r="H26" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="I26" s="13" t="s">
         <v>112</v>
@@ -10247,7 +10247,7 @@
         <v>63</v>
       </c>
       <c r="K26" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L26" s="13" t="s">
         <v>112</v>
@@ -10275,7 +10275,7 @@
         <v>63</v>
       </c>
       <c r="H27" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>112</v>
@@ -10284,7 +10284,7 @@
         <v>63</v>
       </c>
       <c r="K27" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L27" s="13" t="s">
         <v>112</v>
@@ -10312,7 +10312,7 @@
         <v>63</v>
       </c>
       <c r="H28" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="I28" s="13" t="s">
         <v>112</v>
@@ -10321,7 +10321,7 @@
         <v>63</v>
       </c>
       <c r="K28" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L28" s="13" t="s">
         <v>112</v>
@@ -10349,7 +10349,7 @@
         <v>63</v>
       </c>
       <c r="H29" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>112</v>
@@ -10358,7 +10358,7 @@
         <v>63</v>
       </c>
       <c r="K29" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>112</v>
@@ -10386,7 +10386,7 @@
         <v>63</v>
       </c>
       <c r="H30" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>112</v>
@@ -10395,7 +10395,7 @@
         <v>63</v>
       </c>
       <c r="K30" s="12">
-        <v>46282</v>
+        <v>46255</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>112</v>
@@ -10404,14 +10404,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="F7:F9"/>
     <mergeCell ref="A24:M24"/>
     <mergeCell ref="A20:M20"/>
     <mergeCell ref="A14:M14"/>
@@ -10421,6 +10413,14 @@
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="J8:L8"/>
     <mergeCell ref="A10:M10"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="F7:F9"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="J15:J19 J11:J13 J21:J23 J25:J30" xr:uid="{94A6CFB2-D683-4AA4-8062-68BC6FD4A984}">
@@ -10458,25 +10458,25 @@
       <c r="A1" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:13" ht="33.6">
       <c r="A3" s="8"/>
@@ -10542,64 +10542,64 @@
     </row>
     <row r="6" spans="1:13" ht="380.55" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47" t="s">
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47" t="s">
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.05" customHeight="1">
-      <c r="A8" s="47"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47" t="s">
+      <c r="A8" s="48"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47" t="s">
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="47"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="47"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
+      <c r="A9" s="48"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -10618,24 +10618,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="47"/>
+      <c r="M9" s="48"/>
     </row>
     <row r="10" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="49" t="s">
         <v>324</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
     </row>
     <row r="11" spans="1:13" ht="51" thickBot="1">
       <c r="A11" s="28" t="s">
@@ -10660,7 +10660,7 @@
         <v>63</v>
       </c>
       <c r="H11" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>112</v>
@@ -10669,7 +10669,7 @@
         <v>63</v>
       </c>
       <c r="K11" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>112</v>
@@ -10697,7 +10697,7 @@
         <v>63</v>
       </c>
       <c r="H12" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>112</v>
@@ -10706,7 +10706,7 @@
         <v>63</v>
       </c>
       <c r="K12" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>112</v>
@@ -10736,7 +10736,7 @@
         <v>63</v>
       </c>
       <c r="H13" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>112</v>
@@ -10745,7 +10745,7 @@
         <v>63</v>
       </c>
       <c r="K13" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>112</v>
@@ -10753,21 +10753,21 @@
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="49" t="s">
         <v>323</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="49"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="49"/>
     </row>
     <row r="15" spans="1:13" ht="51" thickBot="1">
       <c r="A15" s="28" t="s">
@@ -10790,7 +10790,7 @@
         <v>63</v>
       </c>
       <c r="H15" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>112</v>
@@ -10799,7 +10799,7 @@
         <v>63</v>
       </c>
       <c r="K15" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>112</v>
@@ -10827,7 +10827,7 @@
         <v>63</v>
       </c>
       <c r="H16" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>112</v>
@@ -10836,7 +10836,7 @@
         <v>63</v>
       </c>
       <c r="K16" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>112</v>
@@ -10864,7 +10864,7 @@
         <v>63</v>
       </c>
       <c r="H17" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>112</v>
@@ -10873,7 +10873,7 @@
         <v>63</v>
       </c>
       <c r="K17" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>112</v>
@@ -10901,7 +10901,7 @@
         <v>63</v>
       </c>
       <c r="H18" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>112</v>
@@ -10910,7 +10910,7 @@
         <v>63</v>
       </c>
       <c r="K18" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>112</v>
@@ -10940,7 +10940,7 @@
         <v>63</v>
       </c>
       <c r="H19" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>112</v>
@@ -10949,7 +10949,7 @@
         <v>63</v>
       </c>
       <c r="K19" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>112</v>
@@ -10979,7 +10979,7 @@
         <v>63</v>
       </c>
       <c r="H20" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>112</v>
@@ -10988,7 +10988,7 @@
         <v>63</v>
       </c>
       <c r="K20" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>112</v>
@@ -11018,7 +11018,7 @@
         <v>63</v>
       </c>
       <c r="H21" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>112</v>
@@ -11027,7 +11027,7 @@
         <v>63</v>
       </c>
       <c r="K21" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="L21" s="13" t="s">
         <v>112</v>
@@ -11055,7 +11055,7 @@
         <v>63</v>
       </c>
       <c r="H22" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>112</v>
@@ -11064,7 +11064,7 @@
         <v>63</v>
       </c>
       <c r="K22" s="12">
-        <v>46282</v>
+        <v>46256</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>112</v>
@@ -11073,6 +11073,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="A10:M10"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A7:A9"/>
@@ -11081,13 +11088,6 @@
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="E7:E9"/>
     <mergeCell ref="F7:F9"/>
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="A10:M10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="J15:J22 J11:J13" xr:uid="{1C6342AF-04BF-4066-B849-61FD38371F98}">
@@ -11125,25 +11125,25 @@
       <c r="A1" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:13" ht="33.6">
       <c r="A3" s="8"/>
@@ -11209,64 +11209,64 @@
     </row>
     <row r="6" spans="1:13" ht="380.55" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47" t="s">
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47" t="s">
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.05" customHeight="1">
-      <c r="A8" s="47"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47" t="s">
+      <c r="A8" s="48"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47" t="s">
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="47"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="47"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
+      <c r="A9" s="48"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -11285,24 +11285,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="47"/>
+      <c r="M9" s="48"/>
     </row>
     <row r="10" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="49" t="s">
         <v>375</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
     </row>
     <row r="11" spans="1:13" ht="34.200000000000003" thickBot="1">
       <c r="A11" s="28" t="s">
@@ -11327,7 +11327,7 @@
         <v>63</v>
       </c>
       <c r="H11" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>112</v>
@@ -11336,7 +11336,7 @@
         <v>63</v>
       </c>
       <c r="K11" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>112</v>
@@ -11364,7 +11364,7 @@
         <v>63</v>
       </c>
       <c r="H12" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>112</v>
@@ -11373,7 +11373,7 @@
         <v>63</v>
       </c>
       <c r="K12" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>112</v>
@@ -11403,7 +11403,7 @@
         <v>63</v>
       </c>
       <c r="H13" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>112</v>
@@ -11412,7 +11412,7 @@
         <v>63</v>
       </c>
       <c r="K13" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>112</v>
@@ -11420,21 +11420,21 @@
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="49" t="s">
         <v>385</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="49"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="49"/>
     </row>
     <row r="15" spans="1:13" ht="51" thickBot="1">
       <c r="A15" s="28" t="s">
@@ -11457,7 +11457,7 @@
         <v>63</v>
       </c>
       <c r="H15" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>112</v>
@@ -11466,7 +11466,7 @@
         <v>63</v>
       </c>
       <c r="K15" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>112</v>
@@ -11494,7 +11494,7 @@
         <v>63</v>
       </c>
       <c r="H16" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>112</v>
@@ -11503,7 +11503,7 @@
         <v>63</v>
       </c>
       <c r="K16" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>112</v>
@@ -11531,7 +11531,7 @@
         <v>63</v>
       </c>
       <c r="H17" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>112</v>
@@ -11540,7 +11540,7 @@
         <v>63</v>
       </c>
       <c r="K17" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>112</v>
@@ -11568,7 +11568,7 @@
         <v>63</v>
       </c>
       <c r="H18" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>112</v>
@@ -11577,7 +11577,7 @@
         <v>63</v>
       </c>
       <c r="K18" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>112</v>
@@ -11607,7 +11607,7 @@
         <v>63</v>
       </c>
       <c r="H19" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>112</v>
@@ -11616,7 +11616,7 @@
         <v>63</v>
       </c>
       <c r="K19" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>112</v>
@@ -11644,7 +11644,7 @@
         <v>63</v>
       </c>
       <c r="H20" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>112</v>
@@ -11653,7 +11653,7 @@
         <v>63</v>
       </c>
       <c r="K20" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>112</v>
@@ -11681,7 +11681,7 @@
         <v>63</v>
       </c>
       <c r="H21" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>112</v>
@@ -11690,7 +11690,7 @@
         <v>63</v>
       </c>
       <c r="K21" s="12">
-        <v>46282</v>
+        <v>46257</v>
       </c>
       <c r="L21" s="13" t="s">
         <v>112</v>
@@ -11699,6 +11699,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="A10:M10"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A7:A9"/>
@@ -11707,13 +11714,6 @@
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="E7:E9"/>
     <mergeCell ref="F7:F9"/>
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="A10:M10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="J15:J21 J11:J13" xr:uid="{CB49E59E-08D3-4C06-AF94-5C685B7DB672}">
@@ -11751,25 +11751,25 @@
       <c r="A1" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:13" ht="33.6">
       <c r="A3" s="8"/>
@@ -11835,64 +11835,64 @@
     </row>
     <row r="6" spans="1:13" ht="409.05" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47" t="s">
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47" t="s">
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.05" customHeight="1">
-      <c r="A8" s="47"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47" t="s">
+      <c r="A8" s="48"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47" t="s">
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="47"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="47"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
+      <c r="A9" s="48"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -11911,24 +11911,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="47"/>
+      <c r="M9" s="48"/>
     </row>
     <row r="10" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="49" t="s">
         <v>417</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
     </row>
     <row r="11" spans="1:13" ht="51" thickBot="1">
       <c r="A11" s="28" t="s">
@@ -11953,7 +11953,7 @@
         <v>63</v>
       </c>
       <c r="H11" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>112</v>
@@ -11962,7 +11962,7 @@
         <v>63</v>
       </c>
       <c r="K11" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>112</v>
@@ -11990,7 +11990,7 @@
         <v>63</v>
       </c>
       <c r="H12" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>112</v>
@@ -11999,7 +11999,7 @@
         <v>63</v>
       </c>
       <c r="K12" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>112</v>
@@ -12029,7 +12029,7 @@
         <v>63</v>
       </c>
       <c r="H13" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>112</v>
@@ -12038,7 +12038,7 @@
         <v>63</v>
       </c>
       <c r="K13" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>112</v>
@@ -12046,21 +12046,21 @@
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="49" t="s">
         <v>432</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="49"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="49"/>
     </row>
     <row r="15" spans="1:13" ht="51" thickBot="1">
       <c r="A15" s="28" t="s">
@@ -12083,7 +12083,7 @@
         <v>63</v>
       </c>
       <c r="H15" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>112</v>
@@ -12092,7 +12092,7 @@
         <v>63</v>
       </c>
       <c r="K15" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>112</v>
@@ -12120,7 +12120,7 @@
         <v>63</v>
       </c>
       <c r="H16" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>112</v>
@@ -12129,7 +12129,7 @@
         <v>63</v>
       </c>
       <c r="K16" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>112</v>
@@ -12159,7 +12159,7 @@
         <v>63</v>
       </c>
       <c r="H17" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>112</v>
@@ -12168,7 +12168,7 @@
         <v>63</v>
       </c>
       <c r="K17" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>112</v>
@@ -12196,7 +12196,7 @@
         <v>63</v>
       </c>
       <c r="H18" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>112</v>
@@ -12205,7 +12205,7 @@
         <v>63</v>
       </c>
       <c r="K18" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>112</v>
@@ -12235,7 +12235,7 @@
         <v>63</v>
       </c>
       <c r="H19" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>112</v>
@@ -12244,7 +12244,7 @@
         <v>63</v>
       </c>
       <c r="K19" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>112</v>
@@ -12272,7 +12272,7 @@
         <v>63</v>
       </c>
       <c r="H20" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>112</v>
@@ -12281,7 +12281,7 @@
         <v>63</v>
       </c>
       <c r="K20" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>112</v>
@@ -12311,7 +12311,7 @@
         <v>63</v>
       </c>
       <c r="H21" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>112</v>
@@ -12320,7 +12320,7 @@
         <v>63</v>
       </c>
       <c r="K21" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="L21" s="13" t="s">
         <v>112</v>
@@ -12350,7 +12350,7 @@
         <v>63</v>
       </c>
       <c r="H22" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>112</v>
@@ -12359,7 +12359,7 @@
         <v>63</v>
       </c>
       <c r="K22" s="12">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>112</v>
@@ -12368,6 +12368,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="A10:M10"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A7:A9"/>
@@ -12376,13 +12383,6 @@
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="E7:E9"/>
     <mergeCell ref="F7:F9"/>
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="A10:M10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="J15:J22 J11:J13" xr:uid="{19C7DFFD-D0A4-4044-B0A8-5557B2A09A61}">
@@ -12420,25 +12420,25 @@
       <c r="A1" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:13" ht="33.6">
       <c r="A3" s="8"/>
@@ -12504,64 +12504,64 @@
     </row>
     <row r="6" spans="1:13" ht="409.05" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="48" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="47" t="s">
+      <c r="F7" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="47"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47" t="s">
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47" t="s">
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="47"/>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="47" t="s">
+      <c r="A8" s="48"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="47"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="47" t="s">
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="47"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="47"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
+      <c r="A9" s="48"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -12580,24 +12580,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="47"/>
+      <c r="M9" s="48"/>
     </row>
     <row r="10" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="49" t="s">
         <v>470</v>
       </c>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
     </row>
     <row r="11" spans="1:13" ht="51" thickBot="1">
       <c r="A11" s="28" t="s">
@@ -12622,7 +12622,7 @@
         <v>63</v>
       </c>
       <c r="H11" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>112</v>
@@ -12631,7 +12631,7 @@
         <v>63</v>
       </c>
       <c r="K11" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="L11" s="13" t="s">
         <v>112</v>
@@ -12661,7 +12661,7 @@
         <v>63</v>
       </c>
       <c r="H12" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>112</v>
@@ -12670,7 +12670,7 @@
         <v>63</v>
       </c>
       <c r="K12" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="L12" s="13" t="s">
         <v>112</v>
@@ -12700,7 +12700,7 @@
         <v>63</v>
       </c>
       <c r="H13" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>112</v>
@@ -12709,7 +12709,7 @@
         <v>63</v>
       </c>
       <c r="K13" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>112</v>
@@ -12717,21 +12717,21 @@
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="49" t="s">
         <v>486</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="49"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="49"/>
     </row>
     <row r="15" spans="1:13" ht="51" thickBot="1">
       <c r="A15" s="28" t="s">
@@ -12756,7 +12756,7 @@
         <v>63</v>
       </c>
       <c r="H15" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>112</v>
@@ -12765,7 +12765,7 @@
         <v>63</v>
       </c>
       <c r="K15" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>112</v>
@@ -12795,7 +12795,7 @@
         <v>63</v>
       </c>
       <c r="H16" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="I16" s="13" t="s">
         <v>112</v>
@@ -12804,7 +12804,7 @@
         <v>63</v>
       </c>
       <c r="K16" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="L16" s="13" t="s">
         <v>112</v>
@@ -12834,7 +12834,7 @@
         <v>63</v>
       </c>
       <c r="H17" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>112</v>
@@ -12843,7 +12843,7 @@
         <v>63</v>
       </c>
       <c r="K17" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>112</v>
@@ -12873,7 +12873,7 @@
         <v>63</v>
       </c>
       <c r="H18" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="I18" s="13" t="s">
         <v>112</v>
@@ -12882,7 +12882,7 @@
         <v>63</v>
       </c>
       <c r="K18" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="L18" s="13" t="s">
         <v>112</v>
@@ -12912,7 +12912,7 @@
         <v>63</v>
       </c>
       <c r="H19" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="I19" s="13" t="s">
         <v>112</v>
@@ -12921,7 +12921,7 @@
         <v>63</v>
       </c>
       <c r="K19" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>112</v>
@@ -12951,7 +12951,7 @@
         <v>63</v>
       </c>
       <c r="H20" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="I20" s="13" t="s">
         <v>112</v>
@@ -12960,7 +12960,7 @@
         <v>63</v>
       </c>
       <c r="K20" s="12">
-        <v>46282</v>
+        <v>46259</v>
       </c>
       <c r="L20" s="13" t="s">
         <v>112</v>
@@ -12972,6 +12972,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A14:M14"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="A10:M10"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A7:A9"/>
@@ -12980,13 +12987,6 @@
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="E7:E9"/>
     <mergeCell ref="F7:F9"/>
-    <mergeCell ref="A14:M14"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="A10:M10"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="J15:J20 J11:J13" xr:uid="{BE75E75A-8D4B-4E8C-BA0E-EB0B8874D18F}">

--- a/BaoCao_Final/9.1.TestCaseSprint1.xlsx
+++ b/BaoCao_Final/9.1.TestCaseSprint1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xtung\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="e:\Downloads\Document\BaoCao_Final(1)\BaoCao_Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78825E3B-4E54-4714-BF66-7D74EFDAC939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6491FD6-CF57-4B11-914D-DBA81B656EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trường hợp kiểm thử" sheetId="1" r:id="rId1"/>
@@ -2226,7 +2226,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2341,6 +2341,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -2623,12 +2629,6 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2645,16 +2645,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2684,8 +2684,14 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3833,28 +3839,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="52"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="50"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="53"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="55"/>
+      <c r="A2" s="51"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="53"/>
     </row>
     <row r="3" spans="1:4" ht="37.5" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
@@ -3877,24 +3883,24 @@
       <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="59" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" ht="31.2">
       <c r="A6" s="5">
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="59" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3905,10 +3911,10 @@
       <c r="B7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="59" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3919,24 +3925,24 @@
       <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="59" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" ht="31.2">
       <c r="A9" s="4">
         <v>5</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="38" t="s">
+      <c r="C9" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="59" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3947,10 +3953,10 @@
       <c r="B10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="59" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3961,38 +3967,38 @@
       <c r="B11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="38" t="s">
+      <c r="C11" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="59" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" ht="31.2">
       <c r="A12" s="5">
         <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="59" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" ht="31.2">
       <c r="A13" s="4">
         <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="59" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4003,10 +4009,10 @@
       <c r="B14" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="58" t="s">
         <v>565</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="59" t="s">
         <v>566</v>
       </c>
     </row>
@@ -4017,10 +4023,10 @@
       <c r="B15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="58" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="59" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4031,31 +4037,31 @@
       <c r="B16" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="59" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="25"/>
       <c r="B17" s="26"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="41"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="39"/>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="25"/>
       <c r="B19" s="26"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="41"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D2"/>
     <mergeCell ref="B3:D3"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
@@ -4168,64 +4174,64 @@
     </row>
     <row r="6" spans="1:13" ht="409.05" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48" t="s">
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48" t="s">
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="57" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="48"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48" t="s">
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48" t="s">
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="48"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -4244,24 +4250,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="48"/>
+      <c r="M9" s="57"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="44" t="s">
         <v>520</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
     </row>
     <row r="11" spans="1:13" ht="67.2">
       <c r="A11" s="14" t="s">
@@ -4381,21 +4387,21 @@
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="44" t="s">
         <v>486</v>
       </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="49"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
     </row>
     <row r="15" spans="1:13" ht="50.4">
       <c r="A15" s="14" t="s">
@@ -4645,7 +4651,7 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -4759,64 +4765,64 @@
     </row>
     <row r="6" spans="1:13" ht="409.05" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48" t="s">
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48" t="s">
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="57" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="48"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48" t="s">
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48" t="s">
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="48"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -4835,24 +4841,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="48"/>
+      <c r="M9" s="57"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="44" t="s">
         <v>615</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
     </row>
     <row r="11" spans="1:13" ht="33.6">
       <c r="A11" s="14" t="s">
@@ -5007,21 +5013,21 @@
       <c r="M14" s="8"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="49" t="s">
+      <c r="A15" s="44" t="s">
         <v>616</v>
       </c>
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="49"/>
-      <c r="L15" s="49"/>
-      <c r="M15" s="49"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="44"/>
     </row>
     <row r="16" spans="1:13" ht="33.6">
       <c r="A16" s="14" t="s">
@@ -5273,7 +5279,7 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -5387,64 +5393,64 @@
     </row>
     <row r="6" spans="1:13" ht="409.05" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48" t="s">
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48" t="s">
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="57" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="48"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48" t="s">
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48" t="s">
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="48"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -5463,24 +5469,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="48"/>
+      <c r="M9" s="57"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="44" t="s">
         <v>617</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
     </row>
     <row r="11" spans="1:13" ht="50.4">
       <c r="A11" s="14" t="s">
@@ -5598,21 +5604,21 @@
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="44" t="s">
         <v>632</v>
       </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="49"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
     </row>
     <row r="15" spans="1:13" ht="50.4">
       <c r="A15" s="14" t="s">
@@ -5899,7 +5905,7 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -6013,64 +6019,64 @@
     </row>
     <row r="6" spans="1:13" ht="409.05" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48" t="s">
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48" t="s">
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="57" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="48"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48" t="s">
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48" t="s">
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="48"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -6089,24 +6095,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="48"/>
+      <c r="M9" s="57"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="44" t="s">
         <v>666</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
     </row>
     <row r="11" spans="1:13" ht="33.6">
       <c r="A11" s="14" t="s">
@@ -6261,21 +6267,21 @@
       <c r="M14" s="8"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="49" t="s">
+      <c r="A15" s="44" t="s">
         <v>632</v>
       </c>
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="49"/>
-      <c r="L15" s="49"/>
-      <c r="M15" s="49"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="44"/>
     </row>
     <row r="16" spans="1:13" ht="50.4">
       <c r="A16" s="14" t="s">
@@ -6490,7 +6496,7 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -6599,64 +6605,64 @@
     </row>
     <row r="6" spans="1:13" ht="361.5" customHeight="1"/>
     <row r="7" spans="1:13" ht="16.8">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="59" t="s">
+      <c r="D7" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="59" t="s">
+      <c r="E7" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="59" t="s">
+      <c r="F7" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="59" t="s">
+      <c r="G7" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59" t="s">
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="59"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="59" t="s">
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.8">
-      <c r="A8" s="59"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59" t="s">
+      <c r="A8" s="45"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="59" t="s">
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="59"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="59"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="59"/>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
+      <c r="A9" s="45"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
       <c r="G9" s="16" t="s">
         <v>59</v>
       </c>
@@ -6675,24 +6681,24 @@
       <c r="L9" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="59"/>
+      <c r="M9" s="45"/>
     </row>
     <row r="10" spans="1:13" ht="16.8">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
     </row>
     <row r="11" spans="1:13" ht="50.4">
       <c r="A11" s="11" t="s">
@@ -6919,21 +6925,21 @@
       <c r="M16" s="14"/>
     </row>
     <row r="17" spans="1:13" ht="16.8">
-      <c r="A17" s="58" t="s">
+      <c r="A17" s="56" t="s">
         <v>138</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="58"/>
+      <c r="B17" s="56"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="56"/>
+      <c r="G17" s="56"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="56"/>
+      <c r="K17" s="56"/>
+      <c r="L17" s="56"/>
+      <c r="M17" s="56"/>
     </row>
     <row r="18" spans="1:13" ht="50.4">
       <c r="A18" s="15" t="s">
@@ -7593,7 +7599,7 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -7708,64 +7714,64 @@
     </row>
     <row r="6" spans="1:13" ht="287.55" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="59" t="s">
+      <c r="D7" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="59" t="s">
+      <c r="E7" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="59" t="s">
+      <c r="F7" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="59" t="s">
+      <c r="G7" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59" t="s">
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="59"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="59" t="s">
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="59"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59" t="s">
+      <c r="A8" s="45"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="59" t="s">
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="59"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="59"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
     </row>
     <row r="9" spans="1:13" ht="49.5" customHeight="1">
-      <c r="A9" s="59"/>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
+      <c r="A9" s="45"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
       <c r="G9" s="16" t="s">
         <v>59</v>
       </c>
@@ -7784,24 +7790,24 @@
       <c r="L9" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="59"/>
+      <c r="M9" s="45"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
     </row>
     <row r="11" spans="1:13" ht="50.4">
       <c r="A11" s="11" t="s">
@@ -7954,21 +7960,21 @@
       <c r="M14" s="8"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="49" t="s">
+      <c r="A15" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="49"/>
-      <c r="L15" s="49"/>
-      <c r="M15" s="49"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="44"/>
     </row>
     <row r="16" spans="1:13" ht="50.4">
       <c r="A16" s="14" t="s">
@@ -8267,400 +8273,400 @@
       <c r="M23" s="14"/>
     </row>
     <row r="28" spans="1:13">
-      <c r="A28" s="43"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="43"/>
+      <c r="A28" s="41"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="43"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
+      <c r="A29" s="41"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="44"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
+      <c r="A30" s="42"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="42"/>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="43"/>
-      <c r="B31" s="43"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
+      <c r="A31" s="41"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="43"/>
-      <c r="B32" s="43"/>
-      <c r="C32" s="44"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
+      <c r="A32" s="41"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="44"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="44"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
+      <c r="A33" s="42"/>
+      <c r="B33" s="42"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="44"/>
-      <c r="B34" s="44"/>
-      <c r="C34" s="44"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
+      <c r="A34" s="42"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="44"/>
-      <c r="B35" s="44"/>
-      <c r="C35" s="44"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
+      <c r="A35" s="42"/>
+      <c r="B35" s="42"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="44"/>
-      <c r="B36" s="44"/>
-      <c r="C36" s="44"/>
-      <c r="D36" s="44"/>
-      <c r="E36" s="44"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="44"/>
+      <c r="A36" s="42"/>
+      <c r="B36" s="42"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="43"/>
-      <c r="B37" s="43"/>
-      <c r="C37" s="44"/>
-      <c r="D37" s="44"/>
-      <c r="E37" s="44"/>
-      <c r="F37" s="44"/>
-      <c r="G37" s="44"/>
+      <c r="A37" s="41"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="42"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="44"/>
-      <c r="B38" s="44"/>
-      <c r="C38" s="44"/>
-      <c r="D38" s="44"/>
-      <c r="E38" s="44"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="44"/>
+      <c r="A38" s="42"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="42"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="42"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="44"/>
-      <c r="B39" s="44"/>
-      <c r="C39" s="45"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="44"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="44"/>
+      <c r="A39" s="42"/>
+      <c r="B39" s="42"/>
+      <c r="C39" s="43"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="44"/>
-      <c r="B40" s="44"/>
-      <c r="C40" s="44"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="44"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="44"/>
+      <c r="A40" s="42"/>
+      <c r="B40" s="42"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="44"/>
-      <c r="B41" s="44"/>
-      <c r="C41" s="44"/>
-      <c r="D41" s="44"/>
-      <c r="E41" s="44"/>
-      <c r="F41" s="44"/>
-      <c r="G41" s="44"/>
+      <c r="A41" s="42"/>
+      <c r="B41" s="42"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="44"/>
-      <c r="B42" s="44"/>
-      <c r="C42" s="45"/>
-      <c r="D42" s="44"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="44"/>
+      <c r="A42" s="42"/>
+      <c r="B42" s="42"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="44"/>
-      <c r="B43" s="44"/>
-      <c r="C43" s="44"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="44"/>
+      <c r="A43" s="42"/>
+      <c r="B43" s="42"/>
+      <c r="C43" s="42"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="42"/>
+      <c r="F43" s="42"/>
+      <c r="G43" s="42"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="44"/>
-      <c r="B44" s="44"/>
-      <c r="C44" s="44"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="44"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="44"/>
+      <c r="A44" s="42"/>
+      <c r="B44" s="42"/>
+      <c r="C44" s="42"/>
+      <c r="D44" s="42"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="42"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="44"/>
-      <c r="B45" s="44"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="44"/>
-      <c r="G45" s="44"/>
+      <c r="A45" s="42"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="44"/>
-      <c r="B46" s="44"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="44"/>
-      <c r="F46" s="44"/>
-      <c r="G46" s="44"/>
+      <c r="A46" s="42"/>
+      <c r="B46" s="42"/>
+      <c r="C46" s="42"/>
+      <c r="D46" s="42"/>
+      <c r="E46" s="42"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="42"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="44"/>
-      <c r="B47" s="44"/>
-      <c r="C47" s="44"/>
-      <c r="D47" s="44"/>
-      <c r="E47" s="44"/>
-      <c r="F47" s="44"/>
-      <c r="G47" s="44"/>
+      <c r="A47" s="42"/>
+      <c r="B47" s="42"/>
+      <c r="C47" s="42"/>
+      <c r="D47" s="42"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="42"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="44"/>
-      <c r="B48" s="44"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="44"/>
-      <c r="E48" s="44"/>
-      <c r="F48" s="44"/>
-      <c r="G48" s="44"/>
+      <c r="A48" s="42"/>
+      <c r="B48" s="42"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="42"/>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="44"/>
-      <c r="B49" s="44"/>
-      <c r="C49" s="44"/>
-      <c r="D49" s="44"/>
-      <c r="E49" s="44"/>
-      <c r="F49" s="44"/>
-      <c r="G49" s="44"/>
+      <c r="A49" s="42"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="42"/>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="44"/>
-      <c r="B50" s="44"/>
-      <c r="C50" s="45"/>
-      <c r="D50" s="44"/>
-      <c r="E50" s="44"/>
-      <c r="F50" s="44"/>
-      <c r="G50" s="44"/>
+      <c r="A50" s="42"/>
+      <c r="B50" s="42"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="42"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="42"/>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="44"/>
-      <c r="B51" s="44"/>
-      <c r="C51" s="44"/>
-      <c r="D51" s="44"/>
-      <c r="E51" s="44"/>
-      <c r="F51" s="44"/>
-      <c r="G51" s="44"/>
+      <c r="A51" s="42"/>
+      <c r="B51" s="42"/>
+      <c r="C51" s="42"/>
+      <c r="D51" s="42"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="42"/>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="44"/>
-      <c r="B52" s="44"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="44"/>
-      <c r="E52" s="44"/>
-      <c r="F52" s="44"/>
-      <c r="G52" s="44"/>
+      <c r="A52" s="42"/>
+      <c r="B52" s="42"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="42"/>
+      <c r="E52" s="42"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="42"/>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="44"/>
-      <c r="B53" s="44"/>
-      <c r="C53" s="44"/>
-      <c r="D53" s="44"/>
-      <c r="E53" s="44"/>
-      <c r="F53" s="44"/>
-      <c r="G53" s="44"/>
+      <c r="A53" s="42"/>
+      <c r="B53" s="42"/>
+      <c r="C53" s="42"/>
+      <c r="D53" s="42"/>
+      <c r="E53" s="42"/>
+      <c r="F53" s="42"/>
+      <c r="G53" s="42"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="44"/>
-      <c r="B54" s="44"/>
-      <c r="C54" s="44"/>
-      <c r="D54" s="44"/>
-      <c r="E54" s="44"/>
-      <c r="F54" s="44"/>
-      <c r="G54" s="44"/>
+      <c r="A54" s="42"/>
+      <c r="B54" s="42"/>
+      <c r="C54" s="42"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="42"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="42"/>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="44"/>
-      <c r="B55" s="44"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="44"/>
-      <c r="E55" s="44"/>
-      <c r="F55" s="44"/>
-      <c r="G55" s="44"/>
+      <c r="A55" s="42"/>
+      <c r="B55" s="42"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="42"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="42"/>
+      <c r="G55" s="42"/>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="44"/>
-      <c r="B56" s="44"/>
-      <c r="C56" s="44"/>
-      <c r="D56" s="44"/>
-      <c r="E56" s="44"/>
-      <c r="F56" s="44"/>
-      <c r="G56" s="44"/>
+      <c r="A56" s="42"/>
+      <c r="B56" s="42"/>
+      <c r="C56" s="42"/>
+      <c r="D56" s="42"/>
+      <c r="E56" s="42"/>
+      <c r="F56" s="42"/>
+      <c r="G56" s="42"/>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="44"/>
-      <c r="B57" s="44"/>
-      <c r="C57" s="45"/>
-      <c r="D57" s="44"/>
-      <c r="E57" s="44"/>
-      <c r="F57" s="44"/>
-      <c r="G57" s="44"/>
+      <c r="A57" s="42"/>
+      <c r="B57" s="42"/>
+      <c r="C57" s="43"/>
+      <c r="D57" s="42"/>
+      <c r="E57" s="42"/>
+      <c r="F57" s="42"/>
+      <c r="G57" s="42"/>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="44"/>
-      <c r="B58" s="44"/>
-      <c r="C58" s="44"/>
-      <c r="D58" s="44"/>
-      <c r="E58" s="44"/>
-      <c r="F58" s="44"/>
-      <c r="G58" s="44"/>
+      <c r="A58" s="42"/>
+      <c r="B58" s="42"/>
+      <c r="C58" s="42"/>
+      <c r="D58" s="42"/>
+      <c r="E58" s="42"/>
+      <c r="F58" s="42"/>
+      <c r="G58" s="42"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="44"/>
-      <c r="B59" s="44"/>
-      <c r="C59" s="44"/>
-      <c r="D59" s="44"/>
-      <c r="E59" s="44"/>
-      <c r="F59" s="44"/>
-      <c r="G59" s="44"/>
+      <c r="A59" s="42"/>
+      <c r="B59" s="42"/>
+      <c r="C59" s="42"/>
+      <c r="D59" s="42"/>
+      <c r="E59" s="42"/>
+      <c r="F59" s="42"/>
+      <c r="G59" s="42"/>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="44"/>
-      <c r="B60" s="44"/>
-      <c r="C60" s="45"/>
-      <c r="D60" s="44"/>
-      <c r="E60" s="44"/>
-      <c r="F60" s="44"/>
-      <c r="G60" s="44"/>
+      <c r="A60" s="42"/>
+      <c r="B60" s="42"/>
+      <c r="C60" s="43"/>
+      <c r="D60" s="42"/>
+      <c r="E60" s="42"/>
+      <c r="F60" s="42"/>
+      <c r="G60" s="42"/>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="44"/>
-      <c r="B61" s="44"/>
-      <c r="C61" s="44"/>
-      <c r="D61" s="44"/>
-      <c r="E61" s="44"/>
-      <c r="F61" s="44"/>
-      <c r="G61" s="44"/>
+      <c r="A61" s="42"/>
+      <c r="B61" s="42"/>
+      <c r="C61" s="42"/>
+      <c r="D61" s="42"/>
+      <c r="E61" s="42"/>
+      <c r="F61" s="42"/>
+      <c r="G61" s="42"/>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="44"/>
-      <c r="B62" s="44"/>
-      <c r="C62" s="45"/>
-      <c r="D62" s="44"/>
-      <c r="E62" s="44"/>
-      <c r="F62" s="44"/>
-      <c r="G62" s="44"/>
+      <c r="A62" s="42"/>
+      <c r="B62" s="42"/>
+      <c r="C62" s="43"/>
+      <c r="D62" s="42"/>
+      <c r="E62" s="42"/>
+      <c r="F62" s="42"/>
+      <c r="G62" s="42"/>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="44"/>
-      <c r="B63" s="44"/>
-      <c r="C63" s="44"/>
-      <c r="D63" s="44"/>
-      <c r="E63" s="44"/>
-      <c r="F63" s="44"/>
-      <c r="G63" s="44"/>
+      <c r="A63" s="42"/>
+      <c r="B63" s="42"/>
+      <c r="C63" s="42"/>
+      <c r="D63" s="42"/>
+      <c r="E63" s="42"/>
+      <c r="F63" s="42"/>
+      <c r="G63" s="42"/>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="44"/>
-      <c r="B64" s="44"/>
-      <c r="C64" s="44"/>
-      <c r="D64" s="44"/>
-      <c r="E64" s="44"/>
-      <c r="F64" s="44"/>
-      <c r="G64" s="44"/>
+      <c r="A64" s="42"/>
+      <c r="B64" s="42"/>
+      <c r="C64" s="42"/>
+      <c r="D64" s="42"/>
+      <c r="E64" s="42"/>
+      <c r="F64" s="42"/>
+      <c r="G64" s="42"/>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="44"/>
-      <c r="B65" s="44"/>
-      <c r="C65" s="45"/>
-      <c r="D65" s="44"/>
-      <c r="E65" s="44"/>
-      <c r="F65" s="44"/>
-      <c r="G65" s="44"/>
+      <c r="A65" s="42"/>
+      <c r="B65" s="42"/>
+      <c r="C65" s="43"/>
+      <c r="D65" s="42"/>
+      <c r="E65" s="42"/>
+      <c r="F65" s="42"/>
+      <c r="G65" s="42"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="44"/>
-      <c r="B66" s="44"/>
-      <c r="C66" s="44"/>
-      <c r="D66" s="44"/>
-      <c r="E66" s="44"/>
-      <c r="F66" s="44"/>
-      <c r="G66" s="44"/>
+      <c r="A66" s="42"/>
+      <c r="B66" s="42"/>
+      <c r="C66" s="42"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="42"/>
+      <c r="F66" s="42"/>
+      <c r="G66" s="42"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="44"/>
-      <c r="B67" s="44"/>
-      <c r="C67" s="44"/>
-      <c r="D67" s="44"/>
-      <c r="E67" s="44"/>
-      <c r="F67" s="44"/>
-      <c r="G67" s="44"/>
+      <c r="A67" s="42"/>
+      <c r="B67" s="42"/>
+      <c r="C67" s="42"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="42"/>
+      <c r="F67" s="42"/>
+      <c r="G67" s="42"/>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="44"/>
-      <c r="B68" s="44"/>
-      <c r="C68" s="45"/>
-      <c r="D68" s="44"/>
-      <c r="E68" s="44"/>
-      <c r="F68" s="44"/>
-      <c r="G68" s="44"/>
+      <c r="A68" s="42"/>
+      <c r="B68" s="42"/>
+      <c r="C68" s="43"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="42"/>
+      <c r="F68" s="42"/>
+      <c r="G68" s="42"/>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="44"/>
-      <c r="B69" s="44"/>
-      <c r="C69" s="44"/>
-      <c r="D69" s="44"/>
-      <c r="E69" s="44"/>
-      <c r="F69" s="44"/>
-      <c r="G69" s="44"/>
+      <c r="A69" s="42"/>
+      <c r="B69" s="42"/>
+      <c r="C69" s="42"/>
+      <c r="D69" s="42"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="42"/>
+      <c r="G69" s="42"/>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="44"/>
-      <c r="B70" s="44"/>
-      <c r="C70" s="45"/>
-      <c r="D70" s="44"/>
-      <c r="E70" s="44"/>
-      <c r="F70" s="44"/>
-      <c r="G70" s="44"/>
+      <c r="A70" s="42"/>
+      <c r="B70" s="42"/>
+      <c r="C70" s="43"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="G70" s="42"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="44"/>
-      <c r="B71" s="44"/>
-      <c r="C71" s="44"/>
-      <c r="D71" s="44"/>
-      <c r="E71" s="44"/>
-      <c r="F71" s="44"/>
-      <c r="G71" s="44"/>
+      <c r="A71" s="42"/>
+      <c r="B71" s="42"/>
+      <c r="C71" s="42"/>
+      <c r="D71" s="42"/>
+      <c r="E71" s="42"/>
+      <c r="F71" s="42"/>
+      <c r="G71" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -8687,7 +8693,7 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -8698,19 +8704,19 @@
   <dimension ref="A1:M26"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="18.21875" style="42" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" style="42" customWidth="1"/>
-    <col min="3" max="3" width="33.21875" style="42" customWidth="1"/>
-    <col min="4" max="4" width="35.21875" style="42" customWidth="1"/>
-    <col min="5" max="5" width="54" style="42" customWidth="1"/>
-    <col min="6" max="6" width="34.21875" style="42" customWidth="1"/>
-    <col min="7" max="7" width="7.88671875" style="42" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" style="42" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8" style="42" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" style="42" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.88671875" style="42" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="42" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.77734375" style="42"/>
+    <col min="1" max="1" width="18.21875" style="40" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" style="40" customWidth="1"/>
+    <col min="3" max="3" width="33.21875" style="40" customWidth="1"/>
+    <col min="4" max="4" width="35.21875" style="40" customWidth="1"/>
+    <col min="5" max="5" width="54" style="40" customWidth="1"/>
+    <col min="6" max="6" width="34.21875" style="40" customWidth="1"/>
+    <col min="7" max="7" width="7.88671875" style="40" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" style="40" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="40" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" style="40" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="40" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.77734375" style="40"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="16.8">
@@ -8801,64 +8807,64 @@
     </row>
     <row r="6" spans="1:13" ht="277.05" customHeight="1"/>
     <row r="7" spans="1:13" ht="16.8">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="59" t="s">
+      <c r="D7" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="59" t="s">
+      <c r="E7" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="59" t="s">
+      <c r="F7" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="59" t="s">
+      <c r="G7" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="59"/>
-      <c r="I7" s="59"/>
-      <c r="J7" s="59" t="s">
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="59"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="59" t="s">
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.8">
-      <c r="A8" s="59"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-      <c r="G8" s="59" t="s">
+      <c r="A8" s="45"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="59"/>
-      <c r="I8" s="59"/>
-      <c r="J8" s="59" t="s">
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="59"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="59"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="59"/>
-      <c r="B9" s="59"/>
-      <c r="C9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
+      <c r="A9" s="45"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
       <c r="G9" s="16" t="s">
         <v>59</v>
       </c>
@@ -8877,24 +8883,24 @@
       <c r="L9" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="59"/>
+      <c r="M9" s="45"/>
     </row>
     <row r="10" spans="1:13" ht="16.8">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="44" t="s">
         <v>247</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
     </row>
     <row r="11" spans="1:13" ht="33.6">
       <c r="A11" s="11" t="s">
@@ -9088,21 +9094,21 @@
       <c r="M15" s="8"/>
     </row>
     <row r="16" spans="1:13" ht="16.8">
-      <c r="A16" s="49" t="s">
+      <c r="A16" s="44" t="s">
         <v>246</v>
       </c>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="49"/>
-      <c r="J16" s="49"/>
-      <c r="K16" s="49"/>
-      <c r="L16" s="49"/>
-      <c r="M16" s="49"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="44"/>
+      <c r="M16" s="44"/>
     </row>
     <row r="17" spans="1:13" ht="67.2">
       <c r="A17" s="14" t="s">
@@ -9503,7 +9509,7 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -9617,64 +9623,64 @@
     </row>
     <row r="6" spans="1:13" ht="380.55" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48" t="s">
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48" t="s">
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="57" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.05" customHeight="1">
-      <c r="A8" s="48"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48" t="s">
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48" t="s">
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="48"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -9693,24 +9699,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="48"/>
+      <c r="M9" s="57"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="44" t="s">
         <v>322</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
     </row>
     <row r="11" spans="1:13" ht="33.6">
       <c r="A11" s="14" t="s">
@@ -9828,21 +9834,21 @@
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="44" t="s">
         <v>323</v>
       </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="49"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
     </row>
     <row r="15" spans="1:13" ht="33.6">
       <c r="A15" s="14" t="s">
@@ -10032,21 +10038,21 @@
       <c r="M19" s="8"/>
     </row>
     <row r="20" spans="1:13">
-      <c r="A20" s="49" t="s">
+      <c r="A20" s="44" t="s">
         <v>321</v>
       </c>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-      <c r="K20" s="49"/>
-      <c r="L20" s="49"/>
-      <c r="M20" s="49"/>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="44"/>
+      <c r="M20" s="44"/>
     </row>
     <row r="21" spans="1:13" ht="33.6">
       <c r="A21" s="14" t="s">
@@ -10164,21 +10170,21 @@
       <c r="M23" s="8"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="A24" s="49" t="s">
+      <c r="A24" s="44" t="s">
         <v>320</v>
       </c>
-      <c r="B24" s="49"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
-      <c r="K24" s="49"/>
-      <c r="L24" s="49"/>
-      <c r="M24" s="49"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="44"/>
+      <c r="L24" s="44"/>
+      <c r="M24" s="44"/>
     </row>
     <row r="25" spans="1:13" ht="33.6">
       <c r="A25" s="14" t="s">
@@ -10428,7 +10434,7 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -10542,64 +10548,64 @@
     </row>
     <row r="6" spans="1:13" ht="380.55" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48" t="s">
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48" t="s">
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="57" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.05" customHeight="1">
-      <c r="A8" s="48"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48" t="s">
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48" t="s">
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="48"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -10618,24 +10624,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="48"/>
+      <c r="M9" s="57"/>
     </row>
     <row r="10" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="44" t="s">
         <v>324</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
     </row>
     <row r="11" spans="1:13" ht="51" thickBot="1">
       <c r="A11" s="28" t="s">
@@ -10753,21 +10759,21 @@
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="44" t="s">
         <v>323</v>
       </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="49"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
     </row>
     <row r="15" spans="1:13" ht="51" thickBot="1">
       <c r="A15" s="28" t="s">
@@ -11095,7 +11101,7 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -11209,64 +11215,64 @@
     </row>
     <row r="6" spans="1:13" ht="380.55" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48" t="s">
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48" t="s">
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="57" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.05" customHeight="1">
-      <c r="A8" s="48"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48" t="s">
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48" t="s">
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="48"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -11285,24 +11291,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="48"/>
+      <c r="M9" s="57"/>
     </row>
     <row r="10" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="44" t="s">
         <v>375</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
     </row>
     <row r="11" spans="1:13" ht="34.200000000000003" thickBot="1">
       <c r="A11" s="28" t="s">
@@ -11420,21 +11426,21 @@
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="44" t="s">
         <v>385</v>
       </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="49"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
     </row>
     <row r="15" spans="1:13" ht="51" thickBot="1">
       <c r="A15" s="28" t="s">
@@ -11721,7 +11727,7 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -11835,64 +11841,64 @@
     </row>
     <row r="6" spans="1:13" ht="409.05" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48" t="s">
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48" t="s">
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="57" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.05" customHeight="1">
-      <c r="A8" s="48"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48" t="s">
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48" t="s">
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="48"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -11911,24 +11917,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="48"/>
+      <c r="M9" s="57"/>
     </row>
     <row r="10" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="44" t="s">
         <v>417</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
     </row>
     <row r="11" spans="1:13" ht="51" thickBot="1">
       <c r="A11" s="28" t="s">
@@ -12046,21 +12052,21 @@
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="44" t="s">
         <v>432</v>
       </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="49"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
     </row>
     <row r="15" spans="1:13" ht="51" thickBot="1">
       <c r="A15" s="28" t="s">
@@ -12390,7 +12396,7 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -12504,64 +12510,64 @@
     </row>
     <row r="6" spans="1:13" ht="409.05" customHeight="1"/>
     <row r="7" spans="1:13">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="57" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="57" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48" t="s">
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48" t="s">
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="57" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="48"/>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="48" t="s">
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="48" t="s">
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="K8" s="48"/>
-      <c r="L8" s="48"/>
-      <c r="M8" s="48"/>
+      <c r="K8" s="57"/>
+      <c r="L8" s="57"/>
+      <c r="M8" s="57"/>
     </row>
     <row r="9" spans="1:13" ht="50.4">
-      <c r="A9" s="48"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
       <c r="G9" s="32" t="s">
         <v>59</v>
       </c>
@@ -12580,24 +12586,24 @@
       <c r="L9" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="48"/>
+      <c r="M9" s="57"/>
     </row>
     <row r="10" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="44" t="s">
         <v>470</v>
       </c>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="49"/>
-      <c r="M10" s="49"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
     </row>
     <row r="11" spans="1:13" ht="51" thickBot="1">
       <c r="A11" s="28" t="s">
@@ -12717,21 +12723,21 @@
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13" ht="17.399999999999999" thickBot="1">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="44" t="s">
         <v>486</v>
       </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="49"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
     </row>
     <row r="15" spans="1:13" ht="51" thickBot="1">
       <c r="A15" s="28" t="s">
@@ -12994,7 +13000,7 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="1.1811023622047243" right="0.59055118110236215" top="0.78740157480314954" bottom="0.78740157480314954" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
